--- a/data/fmsForecastOutput/File1/RPT_RPT4864512660729AG_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT4864512660729AG_fmsForecastOutput.xlsx
@@ -1878,7 +1878,7 @@
         <v>422.708400261265</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>453.4289653891627</v>
+        <v>453.4289653891626</v>
       </c>
       <c r="E8" s="149" t="n">
         <v>490.3488409442064</v>
@@ -1928,7 +1928,7 @@
         <v>513.9982774713776</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>551.3533845592119</v>
+        <v>551.3533845592118</v>
       </c>
       <c r="V8" s="149" t="n">
         <v>596.2466311282914</v>
@@ -1943,7 +1943,7 @@
         <v>54.23146379455156</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>61.09161397144499</v>
+        <v>61.09161397144497</v>
       </c>
       <c r="AA8" s="149" t="n">
         <v>69.05488391573338</v>
@@ -2034,7 +2034,7 @@
         <v>1789.993116722509</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>1907.060526656715</v>
+        <v>1907.060526656716</v>
       </c>
       <c r="H9" s="155" t="n">
         <v>100.6068191344661</v>
@@ -2052,7 +2052,7 @@
         <v>155.8688220245749</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>27150333.69995079</v>
+        <v>27150333.6999508</v>
       </c>
       <c r="N9" s="159" t="n">
         <v>29777380.5793108</v>
@@ -2061,7 +2061,7 @@
         <v>33379474.89299651</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>37593461.83309863</v>
+        <v>37593461.83309864</v>
       </c>
       <c r="Q9" s="160" t="n">
         <v>43233490.04570393</v>
@@ -2102,7 +2102,7 @@
         <v>156.5307655939363</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>27150333.69995079</v>
+        <v>27150333.6999508</v>
       </c>
       <c r="AE9" s="159" t="n">
         <v>29777380.5793108</v>
@@ -2111,7 +2111,7 @@
         <v>33379474.89299651</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>37593461.83309863</v>
+        <v>37593461.83309864</v>
       </c>
       <c r="AH9" s="160" t="n">
         <v>43233490.04570393</v>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>554.5851484458284</v>
+        <v>554.5851484458285</v>
       </c>
       <c r="D10" s="162" t="n">
         <v>589.6705171895345</v>
@@ -2185,7 +2185,7 @@
         <v>725.933697424749</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>53.9837077865329</v>
+        <v>53.98370778653291</v>
       </c>
       <c r="I10" s="162" t="n">
         <v>60.05617420664082</v>
@@ -2194,13 +2194,13 @@
         <v>67.48848310922519</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>75.81398770652672</v>
+        <v>75.81398770652673</v>
       </c>
       <c r="L10" s="163" t="n">
         <v>86.67670384981616</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>81267820.92599364</v>
+        <v>81267820.92599365</v>
       </c>
       <c r="N10" s="165" t="n">
         <v>91767337.85418236</v>
@@ -2220,22 +2220,22 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>657.7473465442783</v>
+        <v>657.7473465442785</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>700.0162969523204</v>
+        <v>700.0162969523203</v>
       </c>
       <c r="V10" s="162" t="n">
         <v>753.445552418328</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>801.7190554933302</v>
+        <v>801.7190554933303</v>
       </c>
       <c r="X10" s="163" t="n">
         <v>862.1298323685046</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>64.15926477482589</v>
+        <v>64.1592647748259</v>
       </c>
       <c r="Z10" s="162" t="n">
         <v>71.39265721987168</v>
@@ -2250,7 +2250,7 @@
         <v>103.0884958076134</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>81267820.92599364</v>
+        <v>81267820.92599365</v>
       </c>
       <c r="AE10" s="165" t="n">
         <v>91767337.85418236</v>
@@ -2360,7 +2360,7 @@
         <v>15409873.84807424</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>17947587.93403649</v>
+        <v>17947587.9340365</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>15409873.84807424</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>17947587.93403649</v>
+        <v>17947587.9340365</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>596.5534293517517</v>
+        <v>596.5534293517518</v>
       </c>
       <c r="D12" s="162" t="n">
         <v>634.6461063218512</v>
@@ -2470,7 +2470,7 @@
         <v>683.4020695647991</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>727.7593080038673</v>
+        <v>727.7593080038674</v>
       </c>
       <c r="G12" s="163" t="n">
         <v>783.0657078459391</v>
@@ -2485,13 +2485,13 @@
         <v>73.0525418515298</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>82.13037596366028</v>
+        <v>82.1303759636603</v>
       </c>
       <c r="L12" s="163" t="n">
         <v>93.93500226074984</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>91644669.60373858</v>
+        <v>91644669.60373859</v>
       </c>
       <c r="N12" s="165" t="n">
         <v>103511277.3906772</v>
@@ -2500,7 +2500,7 @@
         <v>117922021.9398713</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>134162779.968471</v>
+        <v>134162779.9684711</v>
       </c>
       <c r="Q12" s="166" t="n">
         <v>155745543.8068264</v>
@@ -2511,22 +2511,22 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>710.6821106954367</v>
+        <v>710.6821106954368</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>756.7222879921242</v>
+        <v>756.7222879921241</v>
       </c>
       <c r="V12" s="162" t="n">
         <v>815.1457969298912</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>868.0855194851914</v>
+        <v>868.0855194851915</v>
       </c>
       <c r="X12" s="163" t="n">
         <v>934.0348403658028</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>69.2858640416473</v>
+        <v>69.28586404164732</v>
       </c>
       <c r="Z12" s="162" t="n">
         <v>77.11907085665004</v>
@@ -2535,13 +2535,13 @@
         <v>86.74241682091798</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>97.53919911746614</v>
+        <v>97.53919911746615</v>
       </c>
       <c r="AC12" s="163" t="n">
         <v>111.5803077632288</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>91644669.60373858</v>
+        <v>91644669.60373859</v>
       </c>
       <c r="AE12" s="165" t="n">
         <v>103511277.3906772</v>
@@ -2550,7 +2550,7 @@
         <v>117922021.9398713</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>134162779.968471</v>
+        <v>134162779.9684711</v>
       </c>
       <c r="AH12" s="166" t="n">
         <v>155745543.8068264</v>
@@ -2603,25 +2603,25 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>1600.346021993753</v>
+        <v>1600.346021993752</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>1563.747862346919</v>
+        <v>1563.747862346918</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>1621.319610285061</v>
+        <v>1621.31961028506</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>1658.83533257231</v>
+        <v>1658.835332572309</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>1722.970589399678</v>
+        <v>1722.970589399677</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>1531.873884588692</v>
+        <v>1531.873884588691</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>1484.226340109034</v>
+        <v>1484.226340109033</v>
       </c>
       <c r="J13" s="156" t="n">
         <v>1531.18784064478</v>
@@ -2633,10 +2633,10 @@
         <v>1640.497096024352</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>8305758.863287354</v>
+        <v>8305758.86328735</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>9094600.965851342</v>
+        <v>9094600.965851337</v>
       </c>
       <c r="O13" s="159" t="n">
         <v>10671201.6267484</v>
@@ -2656,22 +2656,22 @@
         <v>1307.941244282315</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>1278.03006144494</v>
+        <v>1278.030061444939</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>1325.082675441449</v>
+        <v>1325.082675441448</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>1355.743769863644</v>
+        <v>1355.743769863643</v>
       </c>
       <c r="X13" s="157" t="n">
         <v>1408.160651253236</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>1243.282040052269</v>
+        <v>1243.282040052268</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>1203.03500481987</v>
+        <v>1203.035004819869</v>
       </c>
       <c r="AA13" s="156" t="n">
         <v>1240.146584247042</v>
@@ -2683,10 +2683,10 @@
         <v>1330.343972035406</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>8305758.863287354</v>
+        <v>8305758.86328735</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>9094600.965851342</v>
+        <v>9094600.965851337</v>
       </c>
       <c r="AF13" s="159" t="n">
         <v>10671201.6267484</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>629.357055623188</v>
+        <v>629.3570556231879</v>
       </c>
       <c r="D14" s="168" t="n">
         <v>666.6356212146635</v>
@@ -2761,7 +2761,7 @@
         <v>822.255144226933</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>63.44836802871785</v>
+        <v>63.44836802871784</v>
       </c>
       <c r="I14" s="168" t="n">
         <v>70.39757635549209</v>
@@ -2776,7 +2776,7 @@
         <v>102.3665296105765</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>99950428.46702597</v>
+        <v>99950428.46702595</v>
       </c>
       <c r="N14" s="171" t="n">
         <v>112605878.3565285</v>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>738.7135426668658</v>
+        <v>738.7135426668657</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>782.5009634380235</v>
+        <v>782.5009634380234</v>
       </c>
       <c r="V14" s="168" t="n">
         <v>842.0363367652345</v>
@@ -2811,7 +2811,7 @@
         <v>962.3440763524183</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>75.1855082346904</v>
+        <v>75.18550823469039</v>
       </c>
       <c r="Z14" s="168" t="n">
         <v>83.42495941448634</v>
@@ -2826,7 +2826,7 @@
         <v>121.2883344476758</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>99950428.46702597</v>
+        <v>99950428.46702595</v>
       </c>
       <c r="AE14" s="171" t="n">
         <v>112605878.3565285</v>
@@ -4411,7 +4411,7 @@
         <v>434.4801059154825</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>476.8359053527951</v>
+        <v>476.835905352795</v>
       </c>
       <c r="E35" s="149" t="n">
         <v>518.9341468162563</v>
@@ -4426,7 +4426,7 @@
         <v>45.02015467697814</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>51.89362239729681</v>
+        <v>51.8936223972968</v>
       </c>
       <c r="J35" s="149" t="n">
         <v>59.03612083681868</v>
@@ -4441,7 +4441,7 @@
         <v>55624566.64527631</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>65190006.93873837</v>
+        <v>65190006.93873836</v>
       </c>
       <c r="O35" s="152" t="n">
         <v>75230239.72499706</v>
@@ -4461,7 +4461,7 @@
         <v>528.3122500004973</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>579.8153853492291</v>
+        <v>579.815385349229</v>
       </c>
       <c r="V35" s="149" t="n">
         <v>631.0053394249444</v>
@@ -4476,7 +4476,7 @@
         <v>55.74171726619357</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>64.24528929803937</v>
+        <v>64.24528929803935</v>
       </c>
       <c r="AA35" s="149" t="n">
         <v>73.08049754803875</v>
@@ -4491,7 +4491,7 @@
         <v>55624566.64527631</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>65190006.93873837</v>
+        <v>65190006.93873836</v>
       </c>
       <c r="AF35" s="152" t="n">
         <v>75230239.72499706</v>
@@ -4519,10 +4519,10 @@
         <v>1795.876680632538</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>1920.118085648131</v>
+        <v>1920.118085648132</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>2050.845733086104</v>
+        <v>2050.845733086105</v>
       </c>
       <c r="H36" s="155" t="n">
         <v>103.4703428304874</v>
@@ -4540,19 +4540,19 @@
         <v>167.6207462228064</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>27923100.6413326</v>
+        <v>27923100.64133261</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>31342259.08279359</v>
+        <v>31342259.0827936</v>
       </c>
       <c r="O36" s="159" t="n">
         <v>35357811.76988091</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>40326348.34933034</v>
+        <v>40326348.34933035</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>46493132.93799449</v>
+        <v>46493132.9379945</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4569,13 +4569,13 @@
         <v>1819.961403505092</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>1945.869025272295</v>
+        <v>1945.869025272296</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>2078.349877256148</v>
+        <v>2078.349877256149</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>103.8963226318206</v>
+        <v>103.8963226318207</v>
       </c>
       <c r="Z36" s="156" t="n">
         <v>115.7890369759217</v>
@@ -4590,19 +4590,19 @@
         <v>168.3325978529948</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>27923100.6413326</v>
+        <v>27923100.64133261</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>31342259.08279359</v>
+        <v>31342259.0827936</v>
       </c>
       <c r="AF36" s="159" t="n">
         <v>35357811.76988091</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>40326348.34933034</v>
+        <v>40326348.34933035</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>46493132.93799449</v>
+        <v>46493132.9379945</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>570.1431998114101</v>
+        <v>570.1431998114102</v>
       </c>
       <c r="D37" s="162" t="n">
         <v>620.2885750139499</v>
@@ -4621,13 +4621,13 @@
         <v>671.6185601515059</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>723.6695025403207</v>
+        <v>723.6695025403208</v>
       </c>
       <c r="G37" s="163" t="n">
         <v>780.1474554163971</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>55.49813943152216</v>
+        <v>55.49813943152218</v>
       </c>
       <c r="I37" s="162" t="n">
         <v>63.17453159601163</v>
@@ -4636,13 +4636,13 @@
         <v>71.44374705142422</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>81.27306254880529</v>
+        <v>81.2730625488053</v>
       </c>
       <c r="L37" s="163" t="n">
         <v>93.14984301210832</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>83547667.2866089</v>
+        <v>83547667.28660892</v>
       </c>
       <c r="N37" s="165" t="n">
         <v>96532266.02153195</v>
@@ -4662,22 +4662,22 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>676.1994580582427</v>
+        <v>676.1994580582428</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>736.3639501473167</v>
+        <v>736.3639501473166</v>
       </c>
       <c r="V37" s="162" t="n">
         <v>797.6023609373076</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>859.4477736206607</v>
+        <v>859.4477736206608</v>
       </c>
       <c r="X37" s="163" t="n">
         <v>926.5149108615047</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>65.95915635097435</v>
+        <v>65.95915635097437</v>
       </c>
       <c r="Z37" s="162" t="n">
         <v>75.09965026645483</v>
@@ -4692,7 +4692,7 @@
         <v>110.7872908673596</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>83547667.2866089</v>
+        <v>83547667.28660892</v>
       </c>
       <c r="AE37" s="165" t="n">
         <v>96532266.02153195</v>
@@ -4717,7 +4717,7 @@
         <v>1505.91450140669</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>1652.994688405639</v>
+        <v>1652.99468840564</v>
       </c>
       <c r="E38" s="156" t="n">
         <v>1805.530716969094</v>
@@ -4776,13 +4776,13 @@
         <v>2571.146373840159</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>2792.184239587262</v>
+        <v>2792.184239587263</v>
       </c>
       <c r="Y38" s="155" t="n">
         <v>190.3826721926081</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>217.422839395355</v>
+        <v>217.4228393953551</v>
       </c>
       <c r="AA38" s="156" t="n">
         <v>247.525521864773</v>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>613.3034929955601</v>
+        <v>613.3034929955602</v>
       </c>
       <c r="D39" s="162" t="n">
         <v>667.6245002407297</v>
@@ -4825,13 +4825,13 @@
         <v>723.4832799947478</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>780.1958994089556</v>
+        <v>780.1958994089557</v>
       </c>
       <c r="G39" s="163" t="n">
         <v>841.5843802943906</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>60.01591787163949</v>
+        <v>60.0159178716395</v>
       </c>
       <c r="I39" s="162" t="n">
         <v>68.33635548475814</v>
@@ -4840,13 +4840,13 @@
         <v>77.33703912303852</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>88.04804258638639</v>
+        <v>88.04804258638642</v>
       </c>
       <c r="L39" s="163" t="n">
         <v>100.9547856246037</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>94217874.23713829</v>
+        <v>94217874.2371383</v>
       </c>
       <c r="N39" s="165" t="n">
         <v>108890079.2880371</v>
@@ -4866,22 +4866,22 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>730.6366864282426</v>
+        <v>730.6366864282427</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>796.0441800702636</v>
+        <v>796.0441800702635</v>
       </c>
       <c r="V39" s="162" t="n">
         <v>862.9537150982416</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>930.632910070647</v>
+        <v>930.6329100706472</v>
       </c>
       <c r="X39" s="163" t="n">
         <v>1003.835469267256</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>71.23127676616211</v>
+        <v>71.23127676616213</v>
       </c>
       <c r="Z39" s="162" t="n">
         <v>81.12644295274342</v>
@@ -4890,13 +4890,13 @@
         <v>91.82981883012697</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>104.5671039121581</v>
+        <v>104.5671039121582</v>
       </c>
       <c r="AC39" s="163" t="n">
         <v>119.9187286853443</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>94217874.23713829</v>
+        <v>94217874.2371383</v>
       </c>
       <c r="AE39" s="165" t="n">
         <v>108890079.2880371</v>
@@ -4918,46 +4918,46 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>1646.107819372303</v>
+        <v>1646.107819372302</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>1646.223668119717</v>
+        <v>1646.223668119716</v>
       </c>
       <c r="E40" s="156" t="n">
         <v>1717.863541306485</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>1779.866236665569</v>
+        <v>1779.866236665568</v>
       </c>
       <c r="G40" s="157" t="n">
         <v>1853.25437173247</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>1575.67772535352</v>
+        <v>1575.677725353519</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>1562.507990429555</v>
+        <v>1562.507990429554</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>1622.364738975186</v>
+        <v>1622.364738975185</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>1688.103541170757</v>
+        <v>1688.103541170756</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>1764.544579998228</v>
+        <v>1764.544579998227</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930622</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>9574271.992684854</v>
+        <v>9574271.992684849</v>
       </c>
       <c r="O40" s="159" t="n">
         <v>11306634.48479381</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>13406548.40208462</v>
+        <v>13406548.40208461</v>
       </c>
       <c r="Q40" s="160" t="n">
         <v>16037396.42810286</v>
@@ -4977,7 +4977,7 @@
         <v>1403.986729647646</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>1454.660697278588</v>
+        <v>1454.660697278587</v>
       </c>
       <c r="X40" s="157" t="n">
         <v>1514.639831400706</v>
@@ -4989,25 +4989,25 @@
         <v>1266.485950963122</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>1313.992990302016</v>
+        <v>1313.992990302015</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>1368.13111179333</v>
+        <v>1368.131111793329</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>1430.938982505546</v>
+        <v>1430.938982505545</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930622</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>9574271.992684854</v>
+        <v>9574271.992684849</v>
       </c>
       <c r="AF40" s="159" t="n">
         <v>11306634.48479381</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>13406548.40208462</v>
+        <v>13406548.40208461</v>
       </c>
       <c r="AH40" s="160" t="n">
         <v>16037396.42810286</v>
@@ -5073,7 +5073,7 @@
         <v>759.4869158460932</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>823.2116330261814</v>
+        <v>823.2116330261813</v>
       </c>
       <c r="V41" s="186" t="n">
         <v>891.4840498181826</v>
@@ -5383,7 +5383,7 @@
         <v>0.6469532886392042</v>
       </c>
       <c r="G46" s="150" t="n">
-        <v>0.7218229414437762</v>
+        <v>0.7218229414437761</v>
       </c>
       <c r="H46" s="148" t="n">
         <v>0.03044604995358571</v>
@@ -5398,7 +5398,7 @@
         <v>0.07761790026602297</v>
       </c>
       <c r="L46" s="150" t="n">
-        <v>0.09193218454703325</v>
+        <v>0.09193218454703324</v>
       </c>
       <c r="M46" s="151" t="n">
         <v>37617.55922164049</v>
@@ -5433,7 +5433,7 @@
         <v>0.786672031498461</v>
       </c>
       <c r="X46" s="150" t="n">
-        <v>0.8777108482161911</v>
+        <v>0.8777108482161909</v>
       </c>
       <c r="Y46" s="148" t="n">
         <v>0.03769678537450763</v>
@@ -5476,13 +5476,13 @@
         <v>0.1600547166835736</v>
       </c>
       <c r="D47" s="156" t="n">
-        <v>0.337361397272155</v>
+        <v>0.3373613972721549</v>
       </c>
       <c r="E47" s="156" t="n">
         <v>0.3877024883220891</v>
       </c>
       <c r="F47" s="156" t="n">
-        <v>0.4346065578779159</v>
+        <v>0.4346065578779161</v>
       </c>
       <c r="G47" s="157" t="n">
         <v>0.4812619530017866</v>
@@ -5491,13 +5491,13 @@
         <v>0.0109795595065885</v>
       </c>
       <c r="I47" s="156" t="n">
-        <v>0.0234725268415214</v>
+        <v>0.02347252684152139</v>
       </c>
       <c r="J47" s="156" t="n">
-        <v>0.02789966458076688</v>
+        <v>0.02789966458076687</v>
       </c>
       <c r="K47" s="156" t="n">
-        <v>0.03317183482386823</v>
+        <v>0.03317183482386824</v>
       </c>
       <c r="L47" s="157" t="n">
         <v>0.03933474195029458</v>
@@ -5509,10 +5509,10 @@
         <v>6379.860301983941</v>
       </c>
       <c r="O47" s="159" t="n">
-        <v>7633.214325149865</v>
+        <v>7633.214325149864</v>
       </c>
       <c r="P47" s="159" t="n">
-        <v>9127.613337370522</v>
+        <v>9127.613337370525</v>
       </c>
       <c r="Q47" s="160" t="n">
         <v>10910.31646014669</v>
@@ -5526,13 +5526,13 @@
         <v>0.1622012301593269</v>
       </c>
       <c r="U47" s="156" t="n">
-        <v>0.3418857924318134</v>
+        <v>0.3418857924318133</v>
       </c>
       <c r="V47" s="156" t="n">
         <v>0.3929020140406079</v>
       </c>
       <c r="W47" s="156" t="n">
-        <v>0.4404351198376364</v>
+        <v>0.4404351198376366</v>
       </c>
       <c r="X47" s="157" t="n">
         <v>0.4877162161993405</v>
@@ -5544,10 +5544,10 @@
         <v>0.02356938848779979</v>
       </c>
       <c r="AA47" s="156" t="n">
-        <v>0.02801545309329262</v>
+        <v>0.02801545309329261</v>
       </c>
       <c r="AB47" s="156" t="n">
-        <v>0.03331093541204328</v>
+        <v>0.0333109354120433</v>
       </c>
       <c r="AC47" s="157" t="n">
         <v>0.03950178869606637</v>
@@ -5559,10 +5559,10 @@
         <v>6379.860301983941</v>
       </c>
       <c r="AF47" s="159" t="n">
-        <v>7633.214325149865</v>
+        <v>7633.214325149864</v>
       </c>
       <c r="AG47" s="159" t="n">
-        <v>9127.613337370522</v>
+        <v>9127.613337370525</v>
       </c>
       <c r="AH47" s="160" t="n">
         <v>10910.31646014669</v>
@@ -5587,7 +5587,7 @@
         <v>0.6216016942617842</v>
       </c>
       <c r="G48" s="163" t="n">
-        <v>0.6930929696539325</v>
+        <v>0.6930929696539324</v>
       </c>
       <c r="H48" s="161" t="n">
         <v>0.02695641892635235</v>
@@ -5602,7 +5602,7 @@
         <v>0.06981014565466857</v>
       </c>
       <c r="L48" s="163" t="n">
-        <v>0.08275551098426723</v>
+        <v>0.08275551098426721</v>
       </c>
       <c r="M48" s="164" t="n">
         <v>40580.56617332555</v>
@@ -5617,7 +5617,7 @@
         <v>109348.6561513028</v>
       </c>
       <c r="Q48" s="166" t="n">
-        <v>131564.0736708105</v>
+        <v>131564.0736708104</v>
       </c>
       <c r="S48" s="42" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>0.3284419271691335</v>
       </c>
       <c r="U48" s="162" t="n">
-        <v>0.5762007906777677</v>
+        <v>0.5762007906777676</v>
       </c>
       <c r="V48" s="162" t="n">
         <v>0.6555857032121696</v>
@@ -5637,7 +5637,7 @@
         <v>0.7382295237491443</v>
       </c>
       <c r="X48" s="163" t="n">
-        <v>0.8231276876432302</v>
+        <v>0.8231276876432301</v>
       </c>
       <c r="Y48" s="161" t="n">
         <v>0.03203751817337046</v>
@@ -5652,7 +5652,7 @@
         <v>0.08301509798571909</v>
       </c>
       <c r="AC48" s="163" t="n">
-        <v>0.09842484506494797</v>
+        <v>0.09842484506494795</v>
       </c>
       <c r="AD48" s="164" t="n">
         <v>40580.56617332555</v>
@@ -5667,7 +5667,7 @@
         <v>109348.6561513028</v>
       </c>
       <c r="AH48" s="166" t="n">
-        <v>131564.0736708105</v>
+        <v>131564.0736708104</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" thickBot="1">
@@ -5680,10 +5680,10 @@
         <v>0.4306827746401756</v>
       </c>
       <c r="D49" s="156" t="n">
-        <v>0.7620837373530948</v>
+        <v>0.762083737353095</v>
       </c>
       <c r="E49" s="156" t="n">
-        <v>0.8531117349636228</v>
+        <v>0.853111734963623</v>
       </c>
       <c r="F49" s="156" t="n">
         <v>0.9448874590390857</v>
@@ -5695,7 +5695,7 @@
         <v>0.04733568736836367</v>
       </c>
       <c r="I49" s="156" t="n">
-        <v>0.08709167227941159</v>
+        <v>0.08709167227941161</v>
       </c>
       <c r="J49" s="156" t="n">
         <v>0.1015486834971981</v>
@@ -5710,10 +5710,10 @@
         <v>3051.617028155451</v>
       </c>
       <c r="N49" s="159" t="n">
-        <v>5697.349535184228</v>
+        <v>5697.349535184229</v>
       </c>
       <c r="O49" s="159" t="n">
-        <v>6733.132614278483</v>
+        <v>6733.132614278485</v>
       </c>
       <c r="P49" s="159" t="n">
         <v>7971.1991314295</v>
@@ -5745,7 +5745,7 @@
         <v>0.05444833516559641</v>
       </c>
       <c r="Z49" s="156" t="n">
-        <v>0.1002389246587058</v>
+        <v>0.1002389246587059</v>
       </c>
       <c r="AA49" s="156" t="n">
         <v>0.1169555994928262</v>
@@ -5760,10 +5760,10 @@
         <v>3051.617028155451</v>
       </c>
       <c r="AE49" s="159" t="n">
-        <v>5697.349535184228</v>
+        <v>5697.349535184229</v>
       </c>
       <c r="AF49" s="159" t="n">
-        <v>6733.132614278483</v>
+        <v>6733.132614278485</v>
       </c>
       <c r="AG49" s="159" t="n">
         <v>7971.1991314295</v>
@@ -5791,7 +5791,7 @@
         <v>0.636395703158059</v>
       </c>
       <c r="G50" s="163" t="n">
-        <v>0.7090144378704675</v>
+        <v>0.7090144378704674</v>
       </c>
       <c r="H50" s="161" t="n">
         <v>0.02779329872153088</v>
@@ -5806,7 +5806,7 @@
         <v>0.07181964941869433</v>
       </c>
       <c r="L50" s="163" t="n">
-        <v>0.0850519594421696</v>
+        <v>0.08505195944216959</v>
       </c>
       <c r="M50" s="164" t="n">
         <v>43632.18320148101</v>
@@ -5832,7 +5832,7 @@
         <v>0.3383569626684924</v>
       </c>
       <c r="U50" s="162" t="n">
-        <v>0.5938586384580707</v>
+        <v>0.5938586384580706</v>
       </c>
       <c r="V50" s="162" t="n">
         <v>0.6748788808842028</v>
@@ -5841,7 +5841,7 @@
         <v>0.7591052268220135</v>
       </c>
       <c r="X50" s="163" t="n">
-        <v>0.8457070468774528</v>
+        <v>0.8457070468774527</v>
       </c>
       <c r="Y50" s="161" t="n">
         <v>0.03298711781284806</v>
@@ -5995,7 +5995,7 @@
         <v>0.6114140734413246</v>
       </c>
       <c r="G52" s="181" t="n">
-        <v>0.6794520036801073</v>
+        <v>0.6794520036801071</v>
       </c>
       <c r="H52" s="179" t="n">
         <v>0.02769763832055318</v>
@@ -6010,7 +6010,7 @@
         <v>0.07147217195584095</v>
       </c>
       <c r="L52" s="181" t="n">
-        <v>0.08458827426258016</v>
+        <v>0.08458827426258014</v>
       </c>
       <c r="M52" s="182" t="n">
         <v>43632.18320148101</v>
@@ -6036,7 +6036,7 @@
         <v>0.3224767029156769</v>
       </c>
       <c r="U52" s="186" t="n">
-        <v>0.5644923218958644</v>
+        <v>0.5644923218958643</v>
       </c>
       <c r="V52" s="186" t="n">
         <v>0.6392904420103172</v>
@@ -6045,7 +6045,7 @@
         <v>0.7163851232292132</v>
       </c>
       <c r="X52" s="187" t="n">
-        <v>0.7952113349465078</v>
+        <v>0.7952113349465075</v>
       </c>
       <c r="Y52" s="185" t="n">
         <v>0.03282134873963769</v>
@@ -6337,13 +6337,13 @@
         <v>0.008277563575957785</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.007681120878381057</v>
+        <v>0.007681120878381053</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.007176269940001827</v>
+        <v>0.007176269940001829</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.0002645378304486177</v>
+        <v>0.0002645378304486175</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0</v>
@@ -6352,13 +6352,13 @@
         <v>0.0008577082988711825</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.0008359294717032426</v>
+        <v>0.0008359294717032421</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.0008164025087475813</v>
+        <v>0.0008164025087475815</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>3.173779514057276e-05</v>
+        <v>3.173779514057275e-05</v>
       </c>
       <c r="L57" s="150" t="n">
         <v>0</v>
@@ -6370,10 +6370,10 @@
         <v>1050.114552486298</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>1040.348782653505</v>
+        <v>1040.348782653506</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>40.9801722888855</v>
+        <v>40.98017228888548</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6387,13 +6387,13 @@
         <v>0.01006522088766731</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.009339967926109563</v>
+        <v>0.009339967926109558</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.0087260872638224</v>
+        <v>0.008726087263822402</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0003216685286891959</v>
+        <v>0.0003216685286891958</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0.00101062028963005</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>3.928308174442011e-05</v>
+        <v>3.928308174442009e-05</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
@@ -6420,10 +6420,10 @@
         <v>1050.114552486298</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>1040.348782653505</v>
+        <v>1040.348782653506</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>40.9801722888855</v>
+        <v>40.98017228888548</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6541,13 +6541,13 @@
         <v>0.00723184134999208</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.006747734060421266</v>
+        <v>0.006747734060421263</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.006318201125855638</v>
+        <v>0.00631820112585564</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.0002329552590995199</v>
+        <v>0.0002329552590995198</v>
       </c>
       <c r="G59" s="163" t="n">
         <v>0</v>
@@ -6556,13 +6556,13 @@
         <v>0.0007039525153001321</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.0006872364827805836</v>
+        <v>0.0006872364827805832</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.0006721016806828963</v>
+        <v>0.0006721016806828965</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>2.616247786787662e-05</v>
+        <v>2.616247786787661e-05</v>
       </c>
       <c r="L59" s="163" t="n">
         <v>0</v>
@@ -6574,10 +6574,10 @@
         <v>1050.114552486298</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>1040.348782653505</v>
+        <v>1040.348782653506</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>40.9801722888855</v>
+        <v>40.98017228888548</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6591,13 +6591,13 @@
         <v>0.008577085902708979</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.008010445956003061</v>
+        <v>0.008010445956003056</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.007503384262820856</v>
+        <v>0.007503384262820858</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.0002766634189826886</v>
+        <v>0.0002766634189826885</v>
       </c>
       <c r="X59" s="163" t="n">
         <v>0</v>
@@ -6606,13 +6606,13 @@
         <v>0.0008366427144397258</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.0008169624404532772</v>
+        <v>0.0008169624404532769</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.0007991123408984723</v>
+        <v>0.0007991123408984724</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>3.111124670179999e-05</v>
+        <v>3.111124670179998e-05</v>
       </c>
       <c r="AC59" s="163" t="n">
         <v>0</v>
@@ -6624,10 +6624,10 @@
         <v>1050.114552486298</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>1040.348782653505</v>
+        <v>1040.348782653506</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>40.9801722888855</v>
+        <v>40.98017228888548</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6745,13 +6745,13 @@
         <v>0.006898289345998359</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.006438439643750035</v>
+        <v>0.006438439643750032</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.006029208958926719</v>
+        <v>0.00602920895892672</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.0002222949005219428</v>
+        <v>0.0002222949005219427</v>
       </c>
       <c r="G61" s="163" t="n">
         <v>0</v>
@@ -6760,13 +6760,13 @@
         <v>0.0006750445278276612</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.0006590223997229216</v>
+        <v>0.0006590223997229213</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.0006444947409715881</v>
+        <v>0.0006444947409715882</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>2.508681586601515e-05</v>
+        <v>2.508681586601513e-05</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0</v>
@@ -6778,10 +6778,10 @@
         <v>1050.114552486298</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>1040.348782653505</v>
+        <v>1040.348782653506</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>40.9801722888855</v>
+        <v>40.98017228888548</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6795,13 +6795,13 @@
         <v>0.008218024725680107</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.007676893830727931</v>
+        <v>0.007676893830727926</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.007191497597908806</v>
+        <v>0.007191497597908807</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.0002651576999101387</v>
+        <v>0.0002651576999101385</v>
       </c>
       <c r="X61" s="163" t="n">
         <v>0</v>
@@ -6810,13 +6810,13 @@
         <v>0.0008011921719503947</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.000782367492917096</v>
+        <v>0.0007823674929170957</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.0007652715435127103</v>
+        <v>0.0007652715435127104</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>2.979345825789409e-05</v>
+        <v>2.979345825789407e-05</v>
       </c>
       <c r="AC61" s="163" t="n">
         <v>0</v>
@@ -6828,10 +6828,10 @@
         <v>1050.114552486298</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>1040.348782653505</v>
+        <v>1040.348782653506</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>40.9801722888855</v>
+        <v>40.98017228888548</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6949,13 +6949,13 @@
         <v>0.006672855419431157</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.006216760414823191</v>
+        <v>0.006216760414823188</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.005807680867221492</v>
+        <v>0.005807680867221493</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.0002135687434074309</v>
+        <v>0.0002135687434074308</v>
       </c>
       <c r="G63" s="181" t="n">
         <v>0</v>
@@ -6964,13 +6964,13 @@
         <v>0.000672721124950702</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.0006564978708891856</v>
+        <v>0.0006564978708891853</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.0006417241421399778</v>
+        <v>0.0006417241421399779</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>2.496544096097525e-05</v>
+        <v>2.496544096097524e-05</v>
       </c>
       <c r="L63" s="181" t="n">
         <v>0</v>
@@ -6982,10 +6982,10 @@
         <v>1050.114552486298</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>1040.348782653505</v>
+        <v>1040.348782653506</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>40.9801722888855</v>
+        <v>40.98017228888548</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>0</v>
@@ -6999,13 +6999,13 @@
         <v>0.007832324469153324</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.00729727134172456</v>
+        <v>0.007297271341724556</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.006812267813240546</v>
+        <v>0.006812267813240547</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.0002502354414295687</v>
+        <v>0.0002502354414295686</v>
       </c>
       <c r="X63" s="187" t="n">
         <v>0</v>
@@ -7014,13 +7014,13 @@
         <v>0.0007971659674010573</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.0007779857073212184</v>
+        <v>0.0007779857073212181</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.0007604581405741464</v>
+        <v>0.0007604581405741465</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>2.958270500768311e-05</v>
+        <v>2.958270500768309e-05</v>
       </c>
       <c r="AC63" s="187" t="n">
         <v>0</v>
@@ -7032,10 +7032,10 @@
         <v>1050.114552486298</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>1040.348782653505</v>
+        <v>1040.348782653506</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>40.9801722888855</v>
+        <v>40.98017228888548</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>0</v>
@@ -7300,46 +7300,46 @@
         <v>0.003513344942360765</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.005148577945557918</v>
+        <v>0.005148577945557915</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.006873619502767939</v>
+        <v>0.006873619502767943</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.008511598480594228</v>
+        <v>0.008511598480594225</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.01011307601234542</v>
+        <v>0.01011307601234541</v>
       </c>
       <c r="H68" s="148" t="n">
         <v>0.0003640473535730283</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.0005603151037717186</v>
+        <v>0.0005603151037717184</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.0007819717280917416</v>
+        <v>0.0007819717280917421</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.001021174810566009</v>
+        <v>0.001021174810566008</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.00128801277560604</v>
+        <v>0.001288012775606039</v>
       </c>
       <c r="M68" s="151" t="n">
         <v>449.7980166028743</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>703.881205730995</v>
+        <v>703.8812057309947</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>996.4733408741029</v>
+        <v>996.4733408741034</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>1318.551571988936</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>1690.41540215656</v>
+        <v>1690.415402156559</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7350,46 +7350,46 @@
         <v>0.004272101636542021</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.006260486410509581</v>
+        <v>0.006260486410509579</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.008358075170100039</v>
+        <v>0.008358075170100045</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.0103497989508829</v>
+        <v>0.01034979895088289</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.01229713828036027</v>
+        <v>0.01229713828036026</v>
       </c>
       <c r="Y68" s="148" t="n">
         <v>0.0004507453339504128</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.0006936807314062192</v>
+        <v>0.0006936807314062189</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.0009679986108064831</v>
+        <v>0.0009679986108064836</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.00126394708205566</v>
+        <v>0.001263947082055659</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.001593983046297411</v>
+        <v>0.00159398304629741</v>
       </c>
       <c r="AD68" s="151" t="n">
         <v>449.7980166028743</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>703.881205730995</v>
+        <v>703.8812057309947</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>996.4733408741029</v>
+        <v>996.4733408741034</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>1318.551571988936</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>1690.41540215656</v>
+        <v>1690.415402156559</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7504,46 +7504,46 @@
         <v>0.003069496597374089</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.004522938164370782</v>
+        <v>0.004522938164370781</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.006051738694918799</v>
+        <v>0.006051738694918802</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.007495418050550017</v>
+        <v>0.007495418050550013</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.008905280889682407</v>
+        <v>0.0089052808896824</v>
       </c>
       <c r="H70" s="161" t="n">
         <v>0.0002987869542283382</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.000460647691222465</v>
+        <v>0.0004606476912224648</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.0006437566115557645</v>
+        <v>0.0006437566115557649</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.0008417870007142582</v>
+        <v>0.0008417870007142577</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.001063293241673002</v>
+        <v>0.001063293241673001</v>
       </c>
       <c r="M70" s="164" t="n">
         <v>449.7980166028743</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>703.881205730995</v>
+        <v>703.8812057309947</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>996.4733408741029</v>
+        <v>996.4733408741034</v>
       </c>
       <c r="P70" s="165" t="n">
         <v>1318.551571988936</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>1690.41540215656</v>
+        <v>1690.415402156559</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7554,46 +7554,46 @@
         <v>0.003640474772552818</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.005369321227483872</v>
+        <v>0.005369321227483868</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.007186938177756778</v>
+        <v>0.007186938177756782</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.00890174359053137</v>
+        <v>0.008901743590531365</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.01057604619795488</v>
+        <v>0.01057604619795487</v>
       </c>
       <c r="Y70" s="161" t="n">
         <v>0.0003551062365594307</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.0005476016937977746</v>
+        <v>0.0005476016937977743</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.0007654107519958874</v>
+        <v>0.0007654107519958879</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.001001015392419904</v>
+        <v>0.001001015392419903</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.001264622395844641</v>
+        <v>0.00126462239584464</v>
       </c>
       <c r="AD70" s="164" t="n">
         <v>449.7980166028743</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>703.881205730995</v>
+        <v>703.8812057309947</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>996.4733408741029</v>
+        <v>996.4733408741034</v>
       </c>
       <c r="AG70" s="165" t="n">
         <v>1318.551571988936</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>1690.41540215656</v>
+        <v>1690.415402156559</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7606,34 +7606,34 @@
         <v>0.01067464507930155</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.01600814238315598</v>
+        <v>0.01600814238315599</v>
       </c>
       <c r="E71" s="156" t="n">
         <v>0.02175241004797995</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>0.02741749326550369</v>
+        <v>0.0274174932655037</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.03317130369642805</v>
+        <v>0.03317130369642804</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.001173233971719017</v>
+        <v>0.001173233971719018</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.001829426114088587</v>
+        <v>0.001829426114088588</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>0.002589260600614968</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.003443865073796659</v>
+        <v>0.00344386507379666</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.00441027003411957</v>
+        <v>0.004410270034119569</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>75.63555036703737</v>
+        <v>75.63555036703741</v>
       </c>
       <c r="N71" s="159" t="n">
         <v>119.6771143320951</v>
@@ -7642,7 +7642,7 @@
         <v>171.679576696314</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>231.2977026134038</v>
+        <v>231.2977026134039</v>
       </c>
       <c r="Q71" s="160" t="n">
         <v>300.8759082449787</v>
@@ -7653,37 +7653,37 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.01401088132752049</v>
+        <v>0.0140108813275205</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>0.02101130122249693</v>
+        <v>0.02101130122249694</v>
       </c>
       <c r="V71" s="156" t="n">
         <v>0.02855087298038324</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.03598651211232583</v>
+        <v>0.03598651211232585</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.04353860911694169</v>
+        <v>0.04353860911694168</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.001349523796342184</v>
+        <v>0.001349523796342185</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.002105594043830821</v>
+        <v>0.002105594043830822</v>
       </c>
       <c r="AA71" s="156" t="n">
         <v>0.002982101937308073</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.003969996973763161</v>
+        <v>0.003969996973763163</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.005089247570475423</v>
+        <v>0.005089247570475422</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>75.63555036703737</v>
+        <v>75.63555036703741</v>
       </c>
       <c r="AE71" s="159" t="n">
         <v>119.6771143320951</v>
@@ -7692,7 +7692,7 @@
         <v>171.679576696314</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>231.2977026134038</v>
+        <v>231.2977026134039</v>
       </c>
       <c r="AH71" s="160" t="n">
         <v>300.8759082449787</v>
@@ -7708,46 +7708,46 @@
         <v>0.003420266531896986</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.005049382969010484</v>
+        <v>0.005049382969010481</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.006769881556498797</v>
+        <v>0.006769881556498801</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.008407080084804156</v>
+        <v>0.008407080084804152</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.01001192009346404</v>
+        <v>0.01001192009346403</v>
       </c>
       <c r="H72" s="161" t="n">
         <v>0.0003346963414065095</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.0005168420712909198</v>
+        <v>0.0005168420712909196</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.0007236692391800473</v>
+        <v>0.0007236692391800478</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.0009487706176035568</v>
+        <v>0.0009487706176035563</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.001201009988294648</v>
+        <v>0.001201009988294647</v>
       </c>
       <c r="M72" s="164" t="n">
         <v>525.4335669699117</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>823.5583200630902</v>
+        <v>823.5583200630898</v>
       </c>
       <c r="O72" s="165" t="n">
         <v>1168.152917570417</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>1549.84927460234</v>
+        <v>1549.849274602339</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>1991.291310401539</v>
+        <v>1991.291310401537</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7758,46 +7758,46 @@
         <v>0.004074609445579535</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.006020647720353813</v>
+        <v>0.006020647720353809</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.008074954323751772</v>
+        <v>0.008074954323751776</v>
       </c>
       <c r="W72" s="162" t="n">
         <v>0.01002812935885121</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>0.01194214239310512</v>
+        <v>0.01194214239310511</v>
       </c>
       <c r="Y72" s="161" t="n">
         <v>0.0003972420746499146</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.0006135761632987962</v>
+        <v>0.0006135761632987959</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.0008592831569503797</v>
+        <v>0.0008592831569503803</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.001126773439198443</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.001426614796352897</v>
+        <v>0.001426614796352896</v>
       </c>
       <c r="AD72" s="164" t="n">
         <v>525.4335669699117</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>823.5583200630902</v>
+        <v>823.5583200630898</v>
       </c>
       <c r="AF72" s="165" t="n">
         <v>1168.152917570417</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>1549.84927460234</v>
+        <v>1549.849274602339</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>1991.291310401539</v>
+        <v>1991.291310401537</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7912,46 +7912,46 @@
         <v>0.003308493297183484</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.004875529770865936</v>
+        <v>0.004875529770865934</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.00652113931643078</v>
+        <v>0.006521139316430784</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.008077061260611454</v>
+        <v>0.008077061260611451</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.00959447199498646</v>
+        <v>0.009594471994986453</v>
       </c>
       <c r="H74" s="179" t="n">
         <v>0.0003335443663730489</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.000514862195171367</v>
+        <v>0.0005148621951713667</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.0007205582795071693</v>
+        <v>0.0007205582795071697</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.0009441802804228115</v>
+        <v>0.000944180280422811</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.001194462337473155</v>
+        <v>0.001194462337473154</v>
       </c>
       <c r="M74" s="182" t="n">
         <v>525.4335669699117</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>823.5583200630902</v>
+        <v>823.5583200630898</v>
       </c>
       <c r="O74" s="183" t="n">
         <v>1168.152917570417</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>1549.84927460234</v>
+        <v>1549.849274602339</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>1991.291310401539</v>
+        <v>1991.291310401537</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7962,46 +7962,46 @@
         <v>0.003883373964929844</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.005722926620725623</v>
+        <v>0.00572292662072562</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.007649137148996282</v>
+        <v>0.007649137148996286</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.009463777132157118</v>
+        <v>0.009463777132157115</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.01122909762855328</v>
+        <v>0.01122909762855327</v>
       </c>
       <c r="Y74" s="185" t="n">
         <v>0.0003952458271775382</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.0006101397229831434</v>
+        <v>0.0006101397229831432</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.0008538784400132542</v>
+        <v>0.0008538784400132546</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.001118802858458641</v>
+        <v>0.00111880285845864</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.001415251137493169</v>
+        <v>0.001415251137493168</v>
       </c>
       <c r="AD74" s="188" t="n">
         <v>525.4335669699117</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>823.5583200630902</v>
+        <v>823.5583200630898</v>
       </c>
       <c r="AF74" s="189" t="n">
         <v>1168.152917570417</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>1549.84927460234</v>
+        <v>1549.849274602339</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>1991.291310401539</v>
+        <v>1991.291310401537</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8278,7 +8278,7 @@
         <v>45.05182248258416</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>51.95006942965668</v>
+        <v>51.95006942965667</v>
       </c>
       <c r="J79" s="149" t="n">
         <v>59.10305984973107</v>
@@ -8293,7 +8293,7 @@
         <v>55663693.74237496</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>65260917.0479429</v>
+        <v>65260917.04794289</v>
       </c>
       <c r="O79" s="152" t="n">
         <v>75315540.68849149</v>
@@ -8328,7 +8328,7 @@
         <v>55.78092676867524</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>64.31517179527981</v>
+        <v>64.3151717952798</v>
       </c>
       <c r="AA79" s="149" t="n">
         <v>73.16336099332734</v>
@@ -8343,7 +8343,7 @@
         <v>55663693.74237496</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>65260917.0479429</v>
+        <v>65260917.04794289</v>
       </c>
       <c r="AF79" s="152" t="n">
         <v>75315540.68849149</v>
@@ -8371,7 +8371,7 @@
         <v>1796.26438312086</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>1920.552692206009</v>
+        <v>1920.55269220601</v>
       </c>
       <c r="G80" s="157" t="n">
         <v>2051.326995039106</v>
@@ -8389,19 +8389,19 @@
         <v>146.5883464517102</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>167.6600809647566</v>
+        <v>167.6600809647567</v>
       </c>
       <c r="M80" s="158" t="n">
         <v>27926063.64828429</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>31348638.94309557</v>
+        <v>31348638.94309558</v>
       </c>
       <c r="O80" s="159" t="n">
         <v>35365444.98420607</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>40335475.96266771</v>
+        <v>40335475.96266772</v>
       </c>
       <c r="Q80" s="160" t="n">
         <v>46504043.25445464</v>
@@ -8427,7 +8427,7 @@
         <v>2078.837593472348</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>103.9073473933672</v>
+        <v>103.9073473933673</v>
       </c>
       <c r="Z80" s="156" t="n">
         <v>115.8126063644095</v>
@@ -8436,7 +8436,7 @@
         <v>129.7983946047517</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>147.2030403726014</v>
+        <v>147.2030403726015</v>
       </c>
       <c r="AC80" s="157" t="n">
         <v>168.3720996416909</v>
@@ -8445,13 +8445,13 @@
         <v>27926063.64828429</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>31348638.94309557</v>
+        <v>31348638.94309558</v>
       </c>
       <c r="AF80" s="159" t="n">
         <v>35365444.98420607</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>40335475.96266771</v>
+        <v>40335475.96266772</v>
       </c>
       <c r="AH80" s="160" t="n">
         <v>46504043.25445464</v>
@@ -8517,7 +8517,7 @@
         <v>676.5401175460871</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>736.953530705178</v>
+        <v>736.9535307051779</v>
       </c>
       <c r="V81" s="162" t="n">
         <v>798.2726369629605</v>
@@ -8578,7 +8578,7 @@
         <v>1959.883692900946</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>2128.391651352345</v>
+        <v>2128.391651352346</v>
       </c>
       <c r="H82" s="155" t="n">
         <v>165.5612766460949</v>
@@ -8634,7 +8634,7 @@
         <v>190.4384700515701</v>
       </c>
       <c r="Z82" s="156" t="n">
-        <v>217.5251839140575</v>
+        <v>217.5251839140576</v>
       </c>
       <c r="AA82" s="156" t="n">
         <v>247.6454595662032</v>
@@ -8643,7 +8643,7 @@
         <v>283.7871520345784</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>326.5446585939129</v>
+        <v>326.544658593913</v>
       </c>
       <c r="AD82" s="158" t="n">
         <v>10673334.20310791</v>
@@ -8680,7 +8680,7 @@
         <v>780.8409244870991</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>842.3034066523544</v>
+        <v>842.3034066523546</v>
       </c>
       <c r="H83" s="161" t="n">
         <v>60.04472091123026</v>
@@ -8695,7 +8695,7 @@
         <v>88.12083609323857</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>101.0410385940341</v>
+        <v>101.0410385940342</v>
       </c>
       <c r="M83" s="164" t="n">
         <v>94263091.59376715</v>
@@ -8721,7 +8721,7 @@
         <v>730.9873360250824</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>796.6517362502727</v>
+        <v>796.6517362502725</v>
       </c>
       <c r="V83" s="162" t="n">
         <v>863.6438604310474</v>
@@ -8770,46 +8770,46 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>1646.107819372303</v>
+        <v>1646.107819372302</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>1646.223668119717</v>
+        <v>1646.223668119716</v>
       </c>
       <c r="E84" s="156" t="n">
         <v>1717.863541306485</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>1779.866236665569</v>
+        <v>1779.866236665568</v>
       </c>
       <c r="G84" s="157" t="n">
         <v>1853.25437173247</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>1575.67772535352</v>
+        <v>1575.677725353519</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>1562.507990429555</v>
+        <v>1562.507990429554</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>1622.364738975186</v>
+        <v>1622.364738975185</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>1688.103541170757</v>
+        <v>1688.103541170756</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>1764.544579998228</v>
+        <v>1764.544579998227</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930622</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>9574271.992684854</v>
+        <v>9574271.992684849</v>
       </c>
       <c r="O84" s="159" t="n">
         <v>11306634.48479381</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>13406548.40208462</v>
+        <v>13406548.40208461</v>
       </c>
       <c r="Q84" s="160" t="n">
         <v>16037396.42810286</v>
@@ -8829,7 +8829,7 @@
         <v>1403.986729647646</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>1454.660697278588</v>
+        <v>1454.660697278587</v>
       </c>
       <c r="X84" s="157" t="n">
         <v>1514.639831400706</v>
@@ -8841,25 +8841,25 @@
         <v>1266.485950963122</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>1313.992990302016</v>
+        <v>1313.992990302015</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>1368.13111179333</v>
+        <v>1368.131111793329</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>1430.938982505546</v>
+        <v>1430.938982505545</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>8543261.533930626</v>
+        <v>8543261.533930622</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>9574271.992684854</v>
+        <v>9574271.992684849</v>
       </c>
       <c r="AF84" s="159" t="n">
         <v>11306634.48479381</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>13406548.40208462</v>
+        <v>13406548.40208461</v>
       </c>
       <c r="AH84" s="160" t="n">
         <v>16037396.42810286</v>
@@ -8875,7 +8875,7 @@
         <v>647.3399333665789</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>701.8102397959243</v>
+        <v>701.8102397959242</v>
       </c>
       <c r="E85" s="180" t="n">
         <v>760.5766220149645</v>
@@ -8884,13 +8884,13 @@
         <v>820.0575318630433</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>884.4551172220653</v>
+        <v>884.4551172220654</v>
       </c>
       <c r="H85" s="179" t="n">
         <v>65.26130431835443</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>74.11206117830693</v>
+        <v>74.11206117830692</v>
       </c>
       <c r="J85" s="180" t="n">
         <v>84.04049593168891</v>
@@ -8905,7 +8905,7 @@
         <v>102806353.1276978</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>118547458.276878</v>
+        <v>118547458.2768779</v>
       </c>
       <c r="O85" s="183" t="n">
         <v>136244566.6210548</v>
@@ -8925,7 +8925,7 @@
         <v>759.821108247443</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>823.7891455460398</v>
+        <v>823.7891455460395</v>
       </c>
       <c r="V85" s="186" t="n">
         <v>892.1378016651552</v>
@@ -8940,7 +8940,7 @@
         <v>77.3338146540414</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>87.82682609273994</v>
+        <v>87.82682609273992</v>
       </c>
       <c r="AA85" s="186" t="n">
         <v>99.58995629496026</v>
@@ -8949,13 +8949,13 @@
         <v>113.5911541519564</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>130.4632616953038</v>
+        <v>130.4632616953039</v>
       </c>
       <c r="AD85" s="188" t="n">
         <v>102806353.1276978</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>118547458.276878</v>
+        <v>118547458.2768779</v>
       </c>
       <c r="AF85" s="189" t="n">
         <v>136244566.6210548</v>
